--- a/docs/beaverlog_test_cases.xlsx
+++ b/docs/beaverlog_test_cases.xlsx
@@ -4037,7 +4037,7 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>'使い方' タップ → 使い方テキスト表示</t>
+          <t>'使い方' ボタンが設定画面に表示される（タップで外部ブラウザが開くためアプリ内遷移なし）</t>
         </is>
       </c>
     </row>
